--- a/Пробы.xlsx
+++ b/Пробы.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vlada_a\PycharmProjects\sqlite_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filsh\PycharmProjects\PythonProject1\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70732395-45C2-429A-8AD6-CC35A9ECD9E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10980"/>
+    <workbookView xWindow="3660" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,205 +25,28 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>lab_nomer</t>
   </si>
   <si>
-    <t>26_10438</t>
+    <t>25_33333</t>
   </si>
   <si>
-    <t>26_10439</t>
+    <t>25_33334</t>
   </si>
   <si>
-    <t>26_10440</t>
-  </si>
-  <si>
-    <t>26_10441</t>
-  </si>
-  <si>
-    <t>26_10442</t>
-  </si>
-  <si>
-    <t>26_10443</t>
-  </si>
-  <si>
-    <t>26_10444</t>
-  </si>
-  <si>
-    <t>26_10445</t>
-  </si>
-  <si>
-    <t>26_10446</t>
-  </si>
-  <si>
-    <t>26_10447</t>
-  </si>
-  <si>
-    <t>26_10448</t>
-  </si>
-  <si>
-    <t>26_10449</t>
-  </si>
-  <si>
-    <t>26_10450</t>
-  </si>
-  <si>
-    <t>26_10451</t>
-  </si>
-  <si>
-    <t>26_10452</t>
-  </si>
-  <si>
-    <t>26_10453</t>
-  </si>
-  <si>
-    <t>26_10454</t>
-  </si>
-  <si>
-    <t>26_10455</t>
-  </si>
-  <si>
-    <t>26_10456</t>
-  </si>
-  <si>
-    <t>26_10457</t>
-  </si>
-  <si>
-    <t>26_10458</t>
-  </si>
-  <si>
-    <t>26_10459</t>
-  </si>
-  <si>
-    <t>26_10460</t>
-  </si>
-  <si>
-    <t>26_10461</t>
-  </si>
-  <si>
-    <t>26_10462</t>
-  </si>
-  <si>
-    <t>26_10463</t>
-  </si>
-  <si>
-    <t>26_10464</t>
-  </si>
-  <si>
-    <t>26_10465</t>
-  </si>
-  <si>
-    <t>26_10466</t>
-  </si>
-  <si>
-    <t>26_10467</t>
-  </si>
-  <si>
-    <t>26_10468</t>
-  </si>
-  <si>
-    <t>26_10469</t>
-  </si>
-  <si>
-    <t>26_10470</t>
-  </si>
-  <si>
-    <t>26_10471</t>
-  </si>
-  <si>
-    <t>26_10472</t>
-  </si>
-  <si>
-    <t>26_10473</t>
-  </si>
-  <si>
-    <t>26_10474</t>
-  </si>
-  <si>
-    <t>26_10475</t>
-  </si>
-  <si>
-    <t>26_10476</t>
-  </si>
-  <si>
-    <t>26_10477</t>
-  </si>
-  <si>
-    <t>26_10478</t>
-  </si>
-  <si>
-    <t>26_10479</t>
-  </si>
-  <si>
-    <t>26_10480</t>
-  </si>
-  <si>
-    <t>26_10481</t>
-  </si>
-  <si>
-    <t>26_10482</t>
-  </si>
-  <si>
-    <t>26_10483</t>
-  </si>
-  <si>
-    <t>26_10484</t>
-  </si>
-  <si>
-    <t>26_10485</t>
-  </si>
-  <si>
-    <t>26_10486</t>
-  </si>
-  <si>
-    <t>26_10487</t>
-  </si>
-  <si>
-    <t>26_10488</t>
-  </si>
-  <si>
-    <t>26_10489</t>
-  </si>
-  <si>
-    <t>26_10490</t>
-  </si>
-  <si>
-    <t>26_10491</t>
-  </si>
-  <si>
-    <t>26_10492</t>
-  </si>
-  <si>
-    <t>26_10493</t>
-  </si>
-  <si>
-    <t>26_10494</t>
-  </si>
-  <si>
-    <t>26_10495</t>
-  </si>
-  <si>
-    <t>26_10496</t>
-  </si>
-  <si>
-    <t>26_10497</t>
-  </si>
-  <si>
-    <t>26_10498</t>
-  </si>
-  <si>
-    <t>26_10499</t>
+    <t>25_33335</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,6 +214,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="15">
@@ -587,7 +418,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -625,41 +456,41 @@
     </xf>
   </cellXfs>
   <cellStyles count="35">
-    <cellStyle name="Normal 2" xfId="4"/>
-    <cellStyle name="Акцент1 2" xfId="9"/>
-    <cellStyle name="Акцент2 2" xfId="10"/>
-    <cellStyle name="Акцент3 2" xfId="11"/>
-    <cellStyle name="Акцент4 2" xfId="12"/>
-    <cellStyle name="Акцент5 2" xfId="13"/>
-    <cellStyle name="Акцент6 2" xfId="14"/>
-    <cellStyle name="Ввод  2" xfId="15"/>
-    <cellStyle name="Вывод 2" xfId="16"/>
-    <cellStyle name="Вычисление 2" xfId="17"/>
-    <cellStyle name="Заголовок 1 2" xfId="18"/>
-    <cellStyle name="Заголовок 2 2" xfId="19"/>
-    <cellStyle name="Заголовок 3 2" xfId="20"/>
-    <cellStyle name="Заголовок 4 2" xfId="21"/>
-    <cellStyle name="Итог 2" xfId="22"/>
-    <cellStyle name="Контрольная ячейка 2" xfId="23"/>
-    <cellStyle name="Название 2" xfId="24"/>
-    <cellStyle name="Нейтральный 2" xfId="25"/>
+    <cellStyle name="Normal 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Акцент1 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Акцент2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Акцент3 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Акцент4 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Акцент5 2" xfId="13" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Акцент6 2" xfId="14" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Ввод  2" xfId="15" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Вывод 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Вычисление 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Заголовок 1 2" xfId="18" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Заголовок 2 2" xfId="19" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Заголовок 3 2" xfId="20" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Заголовок 4 2" xfId="21" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Итог 2" xfId="22" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Контрольная ячейка 2" xfId="23" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Название 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Нейтральный 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 2 2" xfId="6"/>
-    <cellStyle name="Обычный 2 2 2" xfId="27"/>
-    <cellStyle name="Обычный 2 3" xfId="26"/>
-    <cellStyle name="Обычный 3" xfId="2"/>
-    <cellStyle name="Обычный 3 2" xfId="28"/>
-    <cellStyle name="Обычный 4" xfId="7"/>
-    <cellStyle name="Обычный 5" xfId="8"/>
-    <cellStyle name="Обычный_UDL99" xfId="3"/>
-    <cellStyle name="Плохой 2" xfId="29"/>
-    <cellStyle name="Пояснение 2" xfId="30"/>
-    <cellStyle name="Примечание 2" xfId="31"/>
-    <cellStyle name="Связанная ячейка 2" xfId="32"/>
-    <cellStyle name="Текст предупреждения 2" xfId="33"/>
-    <cellStyle name="Финансовый 2" xfId="5"/>
-    <cellStyle name="Хороший 2" xfId="34"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Обычный 2 2 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Обычный 2 3" xfId="26" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Обычный 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Обычный 3 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Обычный 4" xfId="7" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Обычный 5" xfId="8" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Обычный_UDL99" xfId="3" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Плохой 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Пояснение 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Примечание 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Связанная ячейка 2" xfId="32" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Текст предупреждения 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Финансовый 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Хороший 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -936,326 +767,209 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A63"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>62</v>
-      </c>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="1"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="1"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="1"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>